--- a/backend/data/financials_by_company/000572.SZ.xlsx
+++ b/backend/data/financials_by_company/000572.SZ.xlsx
@@ -682,634 +682,634 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-42958726.9825</v>
+        <v>-9656503.675000001</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>316134880.7</v>
+        <v>756745395.23</v>
       </c>
       <c r="E2" t="n">
-        <v>-171834907.93</v>
+        <v>-38626014.7</v>
       </c>
       <c r="F2" t="n">
-        <v>-171834907.93</v>
+        <v>-38626014.7</v>
       </c>
       <c r="G2" t="n">
-        <v>-139781070.62</v>
+        <v>111678196.66</v>
       </c>
       <c r="H2" t="n">
-        <v>361162761.71</v>
+        <v>567297913.64</v>
       </c>
       <c r="I2" t="n">
-        <v>1606685940.82</v>
+        <v>1433389139.25</v>
       </c>
       <c r="J2" t="n">
-        <v>144299972.77</v>
+        <v>718119380.53</v>
       </c>
       <c r="K2" t="n">
-        <v>-216862788.94</v>
+        <v>150821466.89</v>
       </c>
       <c r="L2" t="n">
-        <v>-10004177.25</v>
+        <v>-2400760.92</v>
       </c>
       <c r="M2" t="n">
-        <v>12187155.5</v>
+        <v>20384442.65</v>
       </c>
       <c r="N2" t="n">
-        <v>4348597.7</v>
+        <v>18895400.05</v>
       </c>
       <c r="O2" t="n">
-        <v>-10904889.6725</v>
+        <v>140647707.685</v>
       </c>
       <c r="P2" t="n">
-        <v>-139781070.62</v>
+        <v>111678196.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2063867370.41</v>
+        <v>2209243584.96</v>
       </c>
       <c r="R2" t="n">
-        <v>-237213682.74</v>
+        <v>1526432.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1644483184</v>
+        <v>1644745164</v>
       </c>
       <c r="T2" t="n">
-        <v>1644483184</v>
+        <v>1644745164</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="W2" t="n">
-        <v>-139781070.62</v>
+        <v>111678196.66</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-139781070.62</v>
+        <v>111678196.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>136689798.25</v>
+        <v>-23263959.93</v>
       </c>
       <c r="AA2" t="n">
-        <v>-276470868.87</v>
+        <v>134942156.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>-276470868.87</v>
+        <v>134942156.59</v>
       </c>
       <c r="AC2" t="n">
-        <v>47420924.43</v>
+        <v>-4505132.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>-229049944.44</v>
+        <v>130437024.24</v>
       </c>
       <c r="AE2" t="n">
-        <v>8163738.3</v>
+        <v>128910591.99</v>
       </c>
       <c r="AF2" t="n">
-        <v>-184198907.93</v>
+        <v>-41520114.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>2327709.99</v>
+        <v>-1301246.01</v>
       </c>
       <c r="AH2" t="n">
-        <v>16567738.45</v>
+        <v>-7235309.07</v>
       </c>
       <c r="AI2" t="n">
-        <v>165303459.49</v>
+        <v>50056669.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-10004177.25</v>
+        <v>-2400760.92</v>
       </c>
       <c r="AK2" t="n">
-        <v>2165619.45</v>
+        <v>911718.3199999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>12187155.5</v>
+        <v>20384442.65</v>
       </c>
       <c r="AM2" t="n">
-        <v>4348597.7</v>
+        <v>18895400.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>-240668872.77</v>
+        <v>-397559160.84</v>
       </c>
       <c r="AO2" t="n">
-        <v>457181429.59</v>
+        <v>775854445.71</v>
       </c>
       <c r="AP2" t="n">
-        <v>39383002.99</v>
+        <v>97144437.39</v>
       </c>
       <c r="AQ2" t="n">
-        <v>58082121.01</v>
+        <v>209045076.92</v>
       </c>
       <c r="AR2" t="n">
-        <v>58082121.01</v>
+        <v>209045076.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>168776790.47</v>
+        <v>245884796.98</v>
       </c>
       <c r="AT2" t="n">
-        <v>122687951.58</v>
+        <v>117893367.18</v>
       </c>
       <c r="AU2" t="n">
-        <v>36177486.54</v>
+        <v>38953360.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>86510465.04000001</v>
+        <v>78940006.76000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>216512556.82</v>
+        <v>378295284.87</v>
       </c>
       <c r="AX2" t="n">
-        <v>1606685940.82</v>
+        <v>1433389139.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1823198497.64</v>
+        <v>1811684424.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1823198497.64</v>
+        <v>1811684424.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-22805391.8425</v>
+        <v>-198209791.5175</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>343621992.88</v>
+        <v>141509715.39</v>
       </c>
       <c r="E3" t="n">
-        <v>-91221567.37</v>
+        <v>-792839166.0700001</v>
       </c>
       <c r="F3" t="n">
-        <v>-91221567.37</v>
+        <v>-792839166.0700001</v>
       </c>
       <c r="G3" t="n">
-        <v>-202044778.45</v>
+        <v>-1574013902.77</v>
       </c>
       <c r="H3" t="n">
-        <v>429263115.84</v>
+        <v>510506587.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2307027560.67</v>
+        <v>2143607031.99</v>
       </c>
       <c r="J3" t="n">
-        <v>252400425.51</v>
+        <v>-651329450.6799999</v>
       </c>
       <c r="K3" t="n">
-        <v>-176862690.33</v>
+        <v>-1161836038.08</v>
       </c>
       <c r="L3" t="n">
-        <v>-11688166.3</v>
+        <v>-3655080.04</v>
       </c>
       <c r="M3" t="n">
-        <v>16540791.94</v>
+        <v>7713388.34</v>
       </c>
       <c r="N3" t="n">
-        <v>6917551.76</v>
+        <v>5933751.17</v>
       </c>
       <c r="O3" t="n">
-        <v>-133628602.9225</v>
+        <v>-979384528.2175</v>
       </c>
       <c r="P3" t="n">
-        <v>-202044778.45</v>
+        <v>-1574013902.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>2793497666.57</v>
+        <v>2799087155.29</v>
       </c>
       <c r="R3" t="n">
-        <v>-272977966.26</v>
+        <v>-1190283301.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1643977042</v>
+        <v>1644565774</v>
       </c>
       <c r="T3" t="n">
-        <v>1643977042</v>
+        <v>1644565774</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1229</v>
+        <v>-0.9571</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1229</v>
+        <v>-0.9571</v>
       </c>
       <c r="W3" t="n">
-        <v>-202044778.45</v>
+        <v>-1574013902.77</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-202044778.45</v>
+        <v>-1574013902.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>-2834102.12</v>
+        <v>936371.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>-199210676.33</v>
+        <v>-1574950273.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>-199210676.33</v>
+        <v>-1574950273.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>5807194.06</v>
+        <v>405400847.48</v>
       </c>
       <c r="AD3" t="n">
-        <v>-193403482.27</v>
+        <v>-1169549426.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>79574483.98999999</v>
+        <v>20733874.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>-74143167.37</v>
+        <v>-772559366.0700001</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3730346.29</v>
+        <v>351379.76</v>
       </c>
       <c r="AH3" t="n">
-        <v>34225967.94</v>
+        <v>-52630996.31</v>
       </c>
       <c r="AI3" t="n">
-        <v>43647545.72</v>
+        <v>824838982.62</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-11688166.3</v>
+        <v>-3655080.04</v>
       </c>
       <c r="AK3" t="n">
-        <v>2064926.12</v>
+        <v>1875442.87</v>
       </c>
       <c r="AL3" t="n">
-        <v>16540791.94</v>
+        <v>7713388.34</v>
       </c>
       <c r="AM3" t="n">
-        <v>6917551.76</v>
+        <v>5933751.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>-209678861.19</v>
+        <v>-389955507.58</v>
       </c>
       <c r="AO3" t="n">
-        <v>486470105.9</v>
+        <v>655480123.3</v>
       </c>
       <c r="AP3" t="n">
-        <v>29401080.06</v>
+        <v>138872400.12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>88416959.65000001</v>
+        <v>89870190.73999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>88416959.65000001</v>
+        <v>89870190.73999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>211927601.3</v>
+        <v>235076948.49</v>
       </c>
       <c r="AT3" t="n">
-        <v>118143387.18</v>
+        <v>126509285.62</v>
       </c>
       <c r="AU3" t="n">
-        <v>40105132.26</v>
+        <v>60675679.32</v>
       </c>
       <c r="AV3" t="n">
-        <v>78038254.92</v>
+        <v>65833606.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>276791244.71</v>
+        <v>265524615.72</v>
       </c>
       <c r="AX3" t="n">
-        <v>2307027560.67</v>
+        <v>2143607031.99</v>
       </c>
       <c r="AY3" t="n">
-        <v>2583818805.38</v>
+        <v>2409131647.71</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2583818805.38</v>
+        <v>2409131647.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-198209791.5175</v>
+        <v>-22805391.8425</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>141509715.39</v>
+        <v>343621992.88</v>
       </c>
       <c r="E4" t="n">
-        <v>-792839166.0700001</v>
+        <v>-91221567.37</v>
       </c>
       <c r="F4" t="n">
-        <v>-792839166.0700001</v>
+        <v>-91221567.37</v>
       </c>
       <c r="G4" t="n">
-        <v>-1574013902.77</v>
+        <v>-202044778.45</v>
       </c>
       <c r="H4" t="n">
-        <v>510506587.4</v>
+        <v>429263115.84</v>
       </c>
       <c r="I4" t="n">
-        <v>2143607031.99</v>
+        <v>2307027560.67</v>
       </c>
       <c r="J4" t="n">
-        <v>-651329450.6799999</v>
+        <v>252400425.51</v>
       </c>
       <c r="K4" t="n">
-        <v>-1161836038.08</v>
+        <v>-176862690.33</v>
       </c>
       <c r="L4" t="n">
-        <v>-3655080.04</v>
+        <v>-11688166.3</v>
       </c>
       <c r="M4" t="n">
-        <v>7713388.34</v>
+        <v>16540791.94</v>
       </c>
       <c r="N4" t="n">
-        <v>5933751.17</v>
+        <v>6917551.76</v>
       </c>
       <c r="O4" t="n">
-        <v>-979384528.2175</v>
+        <v>-133628602.9225</v>
       </c>
       <c r="P4" t="n">
-        <v>-1574013902.77</v>
+        <v>-202044778.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2799087155.29</v>
+        <v>2793497666.57</v>
       </c>
       <c r="R4" t="n">
-        <v>-1190283301.02</v>
+        <v>-272977966.26</v>
       </c>
       <c r="S4" t="n">
-        <v>1644565774</v>
+        <v>1643977042</v>
       </c>
       <c r="T4" t="n">
-        <v>1644565774</v>
+        <v>1643977042</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9571</v>
+        <v>-0.1229</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9571</v>
+        <v>-0.1229</v>
       </c>
       <c r="W4" t="n">
-        <v>-1574013902.77</v>
+        <v>-202044778.45</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1574013902.77</v>
+        <v>-202044778.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>936371.13</v>
+        <v>-2834102.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1574950273.9</v>
+        <v>-199210676.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1574950273.9</v>
+        <v>-199210676.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>405400847.48</v>
+        <v>5807194.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1169549426.42</v>
+        <v>-193403482.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>20733874.6</v>
+        <v>79574483.98999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>-772559366.0700001</v>
+        <v>-74143167.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>351379.76</v>
+        <v>-3730346.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>-52630996.31</v>
+        <v>34225967.94</v>
       </c>
       <c r="AI4" t="n">
-        <v>824838982.62</v>
+        <v>43647545.72</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-3655080.04</v>
+        <v>-11688166.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1875442.87</v>
+        <v>2064926.12</v>
       </c>
       <c r="AL4" t="n">
-        <v>7713388.34</v>
+        <v>16540791.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>5933751.17</v>
+        <v>6917551.76</v>
       </c>
       <c r="AN4" t="n">
-        <v>-389955507.58</v>
+        <v>-209678861.19</v>
       </c>
       <c r="AO4" t="n">
-        <v>655480123.3</v>
+        <v>486470105.9</v>
       </c>
       <c r="AP4" t="n">
-        <v>138872400.12</v>
+        <v>29401080.06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>89870190.73999999</v>
+        <v>88416959.65000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>89870190.73999999</v>
+        <v>88416959.65000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>235076948.49</v>
+        <v>211927601.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>126509285.62</v>
+        <v>118143387.18</v>
       </c>
       <c r="AU4" t="n">
-        <v>60675679.32</v>
+        <v>40105132.26</v>
       </c>
       <c r="AV4" t="n">
-        <v>65833606.3</v>
+        <v>78038254.92</v>
       </c>
       <c r="AW4" t="n">
-        <v>265524615.72</v>
+        <v>276791244.71</v>
       </c>
       <c r="AX4" t="n">
-        <v>2143607031.99</v>
+        <v>2307027560.67</v>
       </c>
       <c r="AY4" t="n">
-        <v>2409131647.71</v>
+        <v>2583818805.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2409131647.71</v>
+        <v>2583818805.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-9656503.675000001</v>
+        <v>-42958726.9825</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>756745395.23</v>
+        <v>316134880.7</v>
       </c>
       <c r="E5" t="n">
-        <v>-38626014.7</v>
+        <v>-171834907.93</v>
       </c>
       <c r="F5" t="n">
-        <v>-38626014.7</v>
+        <v>-171834907.93</v>
       </c>
       <c r="G5" t="n">
-        <v>111678196.66</v>
+        <v>-139781070.62</v>
       </c>
       <c r="H5" t="n">
-        <v>567297913.64</v>
+        <v>361162761.71</v>
       </c>
       <c r="I5" t="n">
-        <v>1433389139.25</v>
+        <v>1606685940.82</v>
       </c>
       <c r="J5" t="n">
-        <v>718119380.53</v>
+        <v>144299972.77</v>
       </c>
       <c r="K5" t="n">
-        <v>150821466.89</v>
+        <v>-216862788.94</v>
       </c>
       <c r="L5" t="n">
-        <v>-2400760.92</v>
+        <v>-10004177.25</v>
       </c>
       <c r="M5" t="n">
-        <v>20384442.65</v>
+        <v>12187155.5</v>
       </c>
       <c r="N5" t="n">
-        <v>18895400.05</v>
+        <v>4348597.7</v>
       </c>
       <c r="O5" t="n">
-        <v>140647707.685</v>
+        <v>-10904889.6725</v>
       </c>
       <c r="P5" t="n">
-        <v>111678196.66</v>
+        <v>-139781070.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>2209243584.96</v>
+        <v>2063867370.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1526432.25</v>
+        <v>-237213682.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1644745164</v>
+        <v>1644483184</v>
       </c>
       <c r="T5" t="n">
-        <v>1644745164</v>
+        <v>1644483184</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0679</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0679</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>111678196.66</v>
+        <v>-139781070.62</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>111678196.66</v>
+        <v>-139781070.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>-23263959.93</v>
+        <v>136689798.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>134942156.59</v>
+        <v>-276470868.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>134942156.59</v>
+        <v>-276470868.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4505132.35</v>
+        <v>47420924.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>130437024.24</v>
+        <v>-229049944.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>128910591.99</v>
+        <v>8163738.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>-41520114.7</v>
+        <v>-184198907.93</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1301246.01</v>
+        <v>2327709.99</v>
       </c>
       <c r="AH5" t="n">
-        <v>-7235309.07</v>
+        <v>16567738.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>50056669.78</v>
+        <v>165303459.49</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2400760.92</v>
+        <v>-10004177.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>911718.3199999999</v>
+        <v>2165619.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>20384442.65</v>
+        <v>12187155.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>18895400.05</v>
+        <v>4348597.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>-397559160.84</v>
+        <v>-240668872.77</v>
       </c>
       <c r="AO5" t="n">
-        <v>775854445.71</v>
+        <v>457181429.59</v>
       </c>
       <c r="AP5" t="n">
-        <v>97144437.39</v>
+        <v>39383002.99</v>
       </c>
       <c r="AQ5" t="n">
-        <v>209045076.92</v>
+        <v>58082121.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>209045076.92</v>
+        <v>58082121.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>245884796.98</v>
+        <v>168776790.47</v>
       </c>
       <c r="AT5" t="n">
-        <v>117893367.18</v>
+        <v>122687951.58</v>
       </c>
       <c r="AU5" t="n">
-        <v>38953360.42</v>
+        <v>36177486.54</v>
       </c>
       <c r="AV5" t="n">
-        <v>78940006.76000001</v>
+        <v>86510465.04000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>378295284.87</v>
+        <v>216512556.82</v>
       </c>
       <c r="AX5" t="n">
-        <v>1433389139.25</v>
+        <v>1606685940.82</v>
       </c>
       <c r="AY5" t="n">
-        <v>1811684424.12</v>
+        <v>1823198497.64</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1811684424.12</v>
+        <v>1823198497.64</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1644636426</v>
@@ -1679,40 +1679,40 @@
         <v>1644636426</v>
       </c>
       <c r="D2" t="n">
-        <v>270276012.48</v>
+        <v>15242517.55</v>
       </c>
       <c r="E2" t="n">
-        <v>1189167802.07</v>
+        <v>2069911038.59</v>
       </c>
       <c r="F2" t="n">
-        <v>1994818350.02</v>
+        <v>3676661004.03</v>
       </c>
       <c r="G2" t="n">
-        <v>231934847.62</v>
+        <v>-261508868.53</v>
       </c>
       <c r="H2" t="n">
-        <v>1189167802.07</v>
+        <v>2069911038.59</v>
       </c>
       <c r="I2" t="n">
-        <v>6233456.7</v>
+        <v>9066979.060000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1756587726.73</v>
+        <v>3676661004.03</v>
       </c>
       <c r="K2" t="n">
-        <v>1756587726.73</v>
+        <v>3676661004.03</v>
       </c>
       <c r="L2" t="n">
-        <v>2504264266.33</v>
+        <v>4552376341.33</v>
       </c>
       <c r="M2" t="n">
-        <v>747676539.6</v>
+        <v>875715337.3</v>
       </c>
       <c r="N2" t="n">
-        <v>1756587726.73</v>
+        <v>3676661004.03</v>
       </c>
       <c r="O2" t="n">
-        <v>-3822081577.12</v>
+        <v>-1897557813.78</v>
       </c>
       <c r="P2" t="n">
         <v>3715207857.7</v>
@@ -1724,160 +1724,156 @@
         <v>1644636426</v>
       </c>
       <c r="S2" t="n">
-        <v>3076303397.46</v>
+        <v>3654895111.22</v>
       </c>
       <c r="T2" t="n">
-        <v>181639743.9</v>
+        <v>211928916.68</v>
       </c>
       <c r="U2" t="n">
-        <v>87090003.92</v>
+        <v>109361469.3</v>
       </c>
       <c r="V2" t="n">
-        <v>83814795.95</v>
+        <v>92057859.56</v>
       </c>
       <c r="W2" t="n">
-        <v>4501487.33</v>
+        <v>1442608.76</v>
       </c>
       <c r="X2" t="n">
-        <v>6233456.7</v>
+        <v>9066979.060000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>6233456.7</v>
+        <v>9066979.060000001</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>2894663653.56</v>
+        <v>3442966194.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>7342367.86</v>
+        <v>46309120.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>264042555.78</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>238230623.29</v>
-      </c>
+        <v>6175538.49</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>1583573715.54</v>
+        <v>2104148493.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>621169122.25</v>
+        <v>749282938.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>446746.31</v>
+        <v>456994.89</v>
       </c>
       <c r="AH2" t="n">
-        <v>19246866.36</v>
+        <v>65730937.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>942710980.62</v>
+        <v>1288677622.46</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5580567663.79</v>
+        <v>8207271452.55</v>
       </c>
       <c r="AK2" t="n">
-        <v>2453969162.61</v>
+        <v>5025814126.54</v>
       </c>
       <c r="AL2" t="n">
-        <v>3072195.2</v>
+        <v>17677893.22</v>
       </c>
       <c r="AM2" t="n">
-        <v>87865510</v>
+        <v>516960217.85</v>
       </c>
       <c r="AN2" t="n">
-        <v>446302091.56</v>
+        <v>449294117.16</v>
       </c>
       <c r="AO2" t="n">
-        <v>446302091.56</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>66613718.84</v>
-      </c>
+        <v>449294117.16</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>3438867.61</v>
+        <v>27881379.79</v>
       </c>
       <c r="AR2" t="n">
-        <v>567419924.66</v>
+        <v>1606749965.44</v>
       </c>
       <c r="AS2" t="n">
-        <v>567419924.66</v>
+        <v>1606749965.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>1275598682.63</v>
+        <v>2291948491.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>-5688077382.51</v>
+        <v>-5458680280.39</v>
       </c>
       <c r="AV2" t="n">
-        <v>6963676065.14</v>
+        <v>7750628772.14</v>
       </c>
       <c r="AW2" t="n">
-        <v>28228095.66</v>
+        <v>45598707.51</v>
       </c>
       <c r="AX2" t="n">
-        <v>487668846.07</v>
+        <v>495000410.68</v>
       </c>
       <c r="AY2" t="n">
-        <v>5226187941.58</v>
+        <v>5659548868.72</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1221591181.83</v>
+        <v>1550480785.23</v>
       </c>
       <c r="BA2" t="n">
-        <v>3126598501.18</v>
+        <v>3181457326.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>46669809.25</v>
+        <v>211653552.51</v>
       </c>
       <c r="BC2" t="n">
-        <v>16179527.92</v>
+        <v>103875787.24</v>
       </c>
       <c r="BD2" t="n">
-        <v>426613687.95</v>
+        <v>717646315.24</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>5441009.24</v>
+        <v>211226410.35</v>
       </c>
       <c r="BG2" t="n">
-        <v>39564538.51</v>
+        <v>245418368.14</v>
       </c>
       <c r="BH2" t="n">
-        <v>145334771.58</v>
+        <v>122527726.94</v>
       </c>
       <c r="BI2" t="n">
-        <v>236273368.62</v>
+        <v>138473809.81</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1701626860.63</v>
+        <v>1149509142.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>570964938.95</v>
+        <v>282881198.31</v>
       </c>
       <c r="BL2" t="n">
-        <v>-177139860.31</v>
+        <v>-113828465.04</v>
       </c>
       <c r="BM2" t="n">
-        <v>748104799.26</v>
+        <v>396709663.35</v>
       </c>
       <c r="BN2" t="n">
-        <v>364543676.48</v>
+        <v>715891330.24</v>
       </c>
       <c r="BO2" t="n">
-        <v>364543676.48</v>
+        <v>715891330.24</v>
       </c>
       <c r="BP2" t="n">
-        <v>165846935.08</v>
+        <v>421488839.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>198696741.4</v>
+        <v>294402490.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1644636426</v>
@@ -1886,40 +1882,40 @@
         <v>1644636426</v>
       </c>
       <c r="D3" t="n">
-        <v>210061627.07</v>
+        <v>110349844.73</v>
       </c>
       <c r="E3" t="n">
-        <v>1062873470.92</v>
+        <v>1170280613.69</v>
       </c>
       <c r="F3" t="n">
-        <v>2082630170.63</v>
+        <v>2100768174.75</v>
       </c>
       <c r="G3" t="n">
-        <v>-203006613.17</v>
+        <v>-242054796.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1062873470.92</v>
+        <v>1170280613.69</v>
       </c>
       <c r="I3" t="n">
-        <v>8539199.5</v>
+        <v>4821425.02</v>
       </c>
       <c r="J3" t="n">
-        <v>1897274441.93</v>
+        <v>2100768174.75</v>
       </c>
       <c r="K3" t="n">
-        <v>1903930170.63</v>
+        <v>2100768174.75</v>
       </c>
       <c r="L3" t="n">
-        <v>2774827945.47</v>
+        <v>2975487576.17</v>
       </c>
       <c r="M3" t="n">
-        <v>877553503.54</v>
+        <v>874719401.42</v>
       </c>
       <c r="N3" t="n">
-        <v>1897274441.93</v>
+        <v>2100768174.75</v>
       </c>
       <c r="O3" t="n">
-        <v>-3682300506.5</v>
+        <v>-3480255728.05</v>
       </c>
       <c r="P3" t="n">
         <v>3715207857.7</v>
@@ -1931,162 +1927,156 @@
         <v>1644636426</v>
       </c>
       <c r="S3" t="n">
-        <v>4584860135</v>
+        <v>3325485410.49</v>
       </c>
       <c r="T3" t="n">
-        <v>171822757.02</v>
+        <v>176686792.53</v>
       </c>
       <c r="U3" t="n">
-        <v>87554504.68000001</v>
+        <v>92431973.81999999</v>
       </c>
       <c r="V3" t="n">
-        <v>64156320.7</v>
+        <v>75814984.90000001</v>
       </c>
       <c r="W3" t="n">
-        <v>4917003.44</v>
+        <v>3618408.79</v>
       </c>
       <c r="X3" t="n">
-        <v>15194928.2</v>
+        <v>4821425.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>8539199.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6655728.7</v>
-      </c>
+        <v>4821425.02</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>4413037377.98</v>
+        <v>3148798617.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>5247071.66</v>
+        <v>6799745.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>194866698.87</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>178700000</v>
-      </c>
+        <v>105528419.71</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>2368569634.84</v>
+        <v>1961321041.86</v>
       </c>
       <c r="AF3" t="n">
-        <v>855699406.59</v>
+        <v>752652252.98</v>
       </c>
       <c r="AG3" t="n">
         <v>456994.89</v>
       </c>
       <c r="AH3" t="n">
-        <v>41436610.47</v>
+        <v>75112919.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1470976622.89</v>
+        <v>1133098874.49</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7359688080.47</v>
+        <v>6300972986.66</v>
       </c>
       <c r="AK3" t="n">
-        <v>3149657315.66</v>
+        <v>3394229165.36</v>
       </c>
       <c r="AL3" t="n">
-        <v>6085239.5</v>
+        <v>9085484.08</v>
       </c>
       <c r="AM3" t="n">
-        <v>129215546.89</v>
+        <v>123006098.81</v>
       </c>
       <c r="AN3" t="n">
-        <v>409059757.97</v>
+        <v>427587112.34</v>
       </c>
       <c r="AO3" t="n">
-        <v>409059757.97</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>88680311.65000001</v>
-      </c>
+        <v>427587112.34</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>23859783.34</v>
+        <v>33256483.28</v>
       </c>
       <c r="AR3" t="n">
-        <v>834400971.01</v>
+        <v>930487561.0599999</v>
       </c>
       <c r="AS3" t="n">
-        <v>834400971.01</v>
+        <v>930487561.0599999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1644113356.03</v>
+        <v>1838095452.47</v>
       </c>
       <c r="AU3" t="n">
-        <v>-5867739748.06</v>
+        <v>-5908282937.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>7511853104.09</v>
+        <v>7746378389.64</v>
       </c>
       <c r="AW3" t="n">
-        <v>35269456.15</v>
+        <v>45522452.02</v>
       </c>
       <c r="AX3" t="n">
-        <v>494970398.2</v>
+        <v>490847435.78</v>
       </c>
       <c r="AY3" t="n">
-        <v>5440948193.94</v>
+        <v>5666572333.97</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1540665055.8</v>
+        <v>1543436167.87</v>
       </c>
       <c r="BA3" t="n">
-        <v>4210030764.81</v>
+        <v>2906743821.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>60181350.08</v>
+        <v>56286718.92</v>
       </c>
       <c r="BC3" t="n">
-        <v>12704208.6</v>
+        <v>152041565.87</v>
       </c>
       <c r="BD3" t="n">
-        <v>911929921.29</v>
+        <v>726366633.23</v>
       </c>
       <c r="BE3" t="n">
-        <v>-4699025.4</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>24702237.19</v>
+        <v>36944132.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>188870648.75</v>
+        <v>212483938.34</v>
       </c>
       <c r="BH3" t="n">
-        <v>384957506.74</v>
+        <v>136592607.59</v>
       </c>
       <c r="BI3" t="n">
-        <v>318098554.01</v>
+        <v>340345954.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2069029198</v>
+        <v>1362170386.36</v>
       </c>
       <c r="BK3" t="n">
-        <v>596104609.78</v>
+        <v>36880348.79</v>
       </c>
       <c r="BL3" t="n">
-        <v>-99567322.45</v>
+        <v>-63414573.06</v>
       </c>
       <c r="BM3" t="n">
-        <v>695671932.23</v>
+        <v>100294921.85</v>
       </c>
       <c r="BN3" t="n">
-        <v>560081477.0599999</v>
+        <v>572998168.13</v>
       </c>
       <c r="BO3" t="n">
-        <v>560081477.0599999</v>
+        <v>572998168.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>398700902.77</v>
+        <v>316530545.22</v>
       </c>
       <c r="BQ3" t="n">
-        <v>161380574.29</v>
+        <v>256467622.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1644636426</v>
@@ -2095,40 +2085,40 @@
         <v>1644636426</v>
       </c>
       <c r="D4" t="n">
-        <v>110349844.73</v>
+        <v>210061627.07</v>
       </c>
       <c r="E4" t="n">
-        <v>1170280613.69</v>
+        <v>1062873470.92</v>
       </c>
       <c r="F4" t="n">
-        <v>2100768174.75</v>
+        <v>2082630170.63</v>
       </c>
       <c r="G4" t="n">
-        <v>-242054796.66</v>
+        <v>-203006613.17</v>
       </c>
       <c r="H4" t="n">
-        <v>1170280613.69</v>
+        <v>1062873470.92</v>
       </c>
       <c r="I4" t="n">
-        <v>4821425.02</v>
+        <v>8539199.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2100768174.75</v>
+        <v>1897274441.93</v>
       </c>
       <c r="K4" t="n">
-        <v>2100768174.75</v>
+        <v>1903930170.63</v>
       </c>
       <c r="L4" t="n">
-        <v>2975487576.17</v>
+        <v>2774827945.47</v>
       </c>
       <c r="M4" t="n">
-        <v>874719401.42</v>
+        <v>877553503.54</v>
       </c>
       <c r="N4" t="n">
-        <v>2100768174.75</v>
+        <v>1897274441.93</v>
       </c>
       <c r="O4" t="n">
-        <v>-3480255728.05</v>
+        <v>-3682300506.5</v>
       </c>
       <c r="P4" t="n">
         <v>3715207857.7</v>
@@ -2140,156 +2130,162 @@
         <v>1644636426</v>
       </c>
       <c r="S4" t="n">
-        <v>3325485410.49</v>
+        <v>4584860135</v>
       </c>
       <c r="T4" t="n">
-        <v>176686792.53</v>
+        <v>171822757.02</v>
       </c>
       <c r="U4" t="n">
-        <v>92431973.81999999</v>
+        <v>87554504.68000001</v>
       </c>
       <c r="V4" t="n">
-        <v>75814984.90000001</v>
+        <v>64156320.7</v>
       </c>
       <c r="W4" t="n">
-        <v>3618408.79</v>
+        <v>4917003.44</v>
       </c>
       <c r="X4" t="n">
-        <v>4821425.02</v>
+        <v>15194928.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4821425.02</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>8539199.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>6655728.7</v>
+      </c>
       <c r="AA4" t="n">
-        <v>3148798617.96</v>
+        <v>4413037377.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>6799745.07</v>
+        <v>5247071.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>105528419.71</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>194866698.87</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>178700000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>1961321041.86</v>
+        <v>2368569634.84</v>
       </c>
       <c r="AF4" t="n">
-        <v>752652252.98</v>
+        <v>855699406.59</v>
       </c>
       <c r="AG4" t="n">
         <v>456994.89</v>
       </c>
       <c r="AH4" t="n">
-        <v>75112919.5</v>
+        <v>41436610.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>1133098874.49</v>
+        <v>1470976622.89</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6300972986.66</v>
+        <v>7359688080.47</v>
       </c>
       <c r="AK4" t="n">
-        <v>3394229165.36</v>
+        <v>3149657315.66</v>
       </c>
       <c r="AL4" t="n">
-        <v>9085484.08</v>
+        <v>6085239.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>123006098.81</v>
+        <v>129215546.89</v>
       </c>
       <c r="AN4" t="n">
-        <v>427587112.34</v>
+        <v>409059757.97</v>
       </c>
       <c r="AO4" t="n">
-        <v>427587112.34</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>409059757.97</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>88680311.65000001</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>33256483.28</v>
+        <v>23859783.34</v>
       </c>
       <c r="AR4" t="n">
-        <v>930487561.0599999</v>
+        <v>834400971.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>930487561.0599999</v>
+        <v>834400971.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1838095452.47</v>
+        <v>1644113356.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>-5908282937.17</v>
+        <v>-5867739748.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>7746378389.64</v>
+        <v>7511853104.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>45522452.02</v>
+        <v>35269456.15</v>
       </c>
       <c r="AX4" t="n">
-        <v>490847435.78</v>
+        <v>494970398.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>5666572333.97</v>
+        <v>5440948193.94</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1543436167.87</v>
+        <v>1540665055.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>2906743821.3</v>
+        <v>4210030764.81</v>
       </c>
       <c r="BB4" t="n">
-        <v>56286718.92</v>
+        <v>60181350.08</v>
       </c>
       <c r="BC4" t="n">
-        <v>152041565.87</v>
+        <v>12704208.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>726366633.23</v>
+        <v>911929921.29</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-4699025.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>36944132.8</v>
+        <v>24702237.19</v>
       </c>
       <c r="BG4" t="n">
-        <v>212483938.34</v>
+        <v>188870648.75</v>
       </c>
       <c r="BH4" t="n">
-        <v>136592607.59</v>
+        <v>384957506.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>340345954.5</v>
+        <v>318098554.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1362170386.36</v>
+        <v>2069029198</v>
       </c>
       <c r="BK4" t="n">
-        <v>36880348.79</v>
+        <v>596104609.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>-63414573.06</v>
+        <v>-99567322.45</v>
       </c>
       <c r="BM4" t="n">
-        <v>100294921.85</v>
+        <v>695671932.23</v>
       </c>
       <c r="BN4" t="n">
-        <v>572998168.13</v>
+        <v>560081477.0599999</v>
       </c>
       <c r="BO4" t="n">
-        <v>572998168.13</v>
+        <v>560081477.0599999</v>
       </c>
       <c r="BP4" t="n">
-        <v>316530545.22</v>
+        <v>398700902.77</v>
       </c>
       <c r="BQ4" t="n">
-        <v>256467622.91</v>
+        <v>161380574.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1644636426</v>
@@ -2298,40 +2294,40 @@
         <v>1644636426</v>
       </c>
       <c r="D5" t="n">
-        <v>15242517.55</v>
+        <v>270276012.48</v>
       </c>
       <c r="E5" t="n">
-        <v>2069911038.59</v>
+        <v>1189167802.07</v>
       </c>
       <c r="F5" t="n">
-        <v>3676661004.03</v>
+        <v>1994818350.02</v>
       </c>
       <c r="G5" t="n">
-        <v>-261508868.53</v>
+        <v>231934847.62</v>
       </c>
       <c r="H5" t="n">
-        <v>2069911038.59</v>
+        <v>1189167802.07</v>
       </c>
       <c r="I5" t="n">
-        <v>9066979.060000001</v>
+        <v>6233456.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3676661004.03</v>
+        <v>1756587726.73</v>
       </c>
       <c r="K5" t="n">
-        <v>3676661004.03</v>
+        <v>1756587726.73</v>
       </c>
       <c r="L5" t="n">
-        <v>4552376341.33</v>
+        <v>2504264266.33</v>
       </c>
       <c r="M5" t="n">
-        <v>875715337.3</v>
+        <v>747676539.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3676661004.03</v>
+        <v>1756587726.73</v>
       </c>
       <c r="O5" t="n">
-        <v>-1897557813.78</v>
+        <v>-3822081577.12</v>
       </c>
       <c r="P5" t="n">
         <v>3715207857.7</v>
@@ -2343,151 +2339,155 @@
         <v>1644636426</v>
       </c>
       <c r="S5" t="n">
-        <v>3654895111.22</v>
+        <v>3076303397.46</v>
       </c>
       <c r="T5" t="n">
-        <v>211928916.68</v>
+        <v>181639743.9</v>
       </c>
       <c r="U5" t="n">
-        <v>109361469.3</v>
+        <v>87090003.92</v>
       </c>
       <c r="V5" t="n">
-        <v>92057859.56</v>
+        <v>83814795.95</v>
       </c>
       <c r="W5" t="n">
-        <v>1442608.76</v>
+        <v>4501487.33</v>
       </c>
       <c r="X5" t="n">
-        <v>9066979.060000001</v>
+        <v>6233456.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>9066979.060000001</v>
+        <v>6233456.7</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>3442966194.54</v>
+        <v>2894663653.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>46309120.85</v>
+        <v>7342367.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>6175538.49</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>264042555.78</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>238230623.29</v>
+      </c>
       <c r="AE5" t="n">
-        <v>2104148493.77</v>
+        <v>1583573715.54</v>
       </c>
       <c r="AF5" t="n">
-        <v>749282938.78</v>
+        <v>621169122.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>456994.89</v>
+        <v>446746.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>65730937.64</v>
+        <v>19246866.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>1288677622.46</v>
+        <v>942710980.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8207271452.55</v>
+        <v>5580567663.79</v>
       </c>
       <c r="AK5" t="n">
-        <v>5025814126.54</v>
+        <v>2453969162.61</v>
       </c>
       <c r="AL5" t="n">
-        <v>17677893.22</v>
+        <v>3072195.2</v>
       </c>
       <c r="AM5" t="n">
-        <v>516960217.85</v>
+        <v>87865510</v>
       </c>
       <c r="AN5" t="n">
-        <v>449294117.16</v>
+        <v>446302091.56</v>
       </c>
       <c r="AO5" t="n">
-        <v>449294117.16</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>446302091.56</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>66613718.84</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>27881379.79</v>
+        <v>3438867.61</v>
       </c>
       <c r="AR5" t="n">
-        <v>1606749965.44</v>
+        <v>567419924.66</v>
       </c>
       <c r="AS5" t="n">
-        <v>1606749965.44</v>
+        <v>567419924.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>2291948491.75</v>
+        <v>1275598682.63</v>
       </c>
       <c r="AU5" t="n">
-        <v>-5458680280.39</v>
+        <v>-5688077382.51</v>
       </c>
       <c r="AV5" t="n">
-        <v>7750628772.14</v>
+        <v>6963676065.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>45598707.51</v>
+        <v>28228095.66</v>
       </c>
       <c r="AX5" t="n">
-        <v>495000410.68</v>
+        <v>487668846.07</v>
       </c>
       <c r="AY5" t="n">
-        <v>5659548868.72</v>
+        <v>5226187941.58</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1550480785.23</v>
+        <v>1221591181.83</v>
       </c>
       <c r="BA5" t="n">
-        <v>3181457326.01</v>
+        <v>3126598501.18</v>
       </c>
       <c r="BB5" t="n">
-        <v>211653552.51</v>
+        <v>46669809.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>103875787.24</v>
+        <v>16179527.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>717646315.24</v>
+        <v>426613687.95</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>211226410.35</v>
+        <v>5441009.24</v>
       </c>
       <c r="BG5" t="n">
-        <v>245418368.14</v>
+        <v>39564538.51</v>
       </c>
       <c r="BH5" t="n">
-        <v>122527726.94</v>
+        <v>145334771.58</v>
       </c>
       <c r="BI5" t="n">
-        <v>138473809.81</v>
+        <v>236273368.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1149509142.47</v>
+        <v>1701626860.63</v>
       </c>
       <c r="BK5" t="n">
-        <v>282881198.31</v>
+        <v>570964938.95</v>
       </c>
       <c r="BL5" t="n">
-        <v>-113828465.04</v>
+        <v>-177139860.31</v>
       </c>
       <c r="BM5" t="n">
-        <v>396709663.35</v>
+        <v>748104799.26</v>
       </c>
       <c r="BN5" t="n">
-        <v>715891330.24</v>
+        <v>364543676.48</v>
       </c>
       <c r="BO5" t="n">
-        <v>715891330.24</v>
+        <v>364543676.48</v>
       </c>
       <c r="BP5" t="n">
-        <v>421488839.86</v>
+        <v>165846935.08</v>
       </c>
       <c r="BQ5" t="n">
-        <v>294402490.38</v>
+        <v>198696741.4</v>
       </c>
     </row>
   </sheetData>
@@ -2753,594 +2753,594 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-876655909.02</v>
+        <v>-132714140.77</v>
       </c>
       <c r="C2" t="n">
-        <v>-230159002.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>279230623.29</v>
-      </c>
+        <v>-424968360.02</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-123647572.16</v>
+        <v>-295718138.41</v>
       </c>
       <c r="F2" t="n">
-        <v>1892427025.43</v>
+        <v>1405460719.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2219565641.13</v>
+        <v>1108979227.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3507312.69</v>
+        <v>-1606605.3</v>
       </c>
       <c r="I2" t="n">
-        <v>-330645928.39</v>
+        <v>298088098.09</v>
       </c>
       <c r="J2" t="n">
-        <v>-147205570.57</v>
+        <v>-526338800.02</v>
       </c>
       <c r="K2" t="n">
-        <v>-187085869.53</v>
+        <v>-86998085</v>
       </c>
       <c r="L2" t="n">
-        <v>-9191322.08</v>
+        <v>-14372355</v>
       </c>
       <c r="M2" t="n">
-        <v>49071621.04</v>
+        <v>-424968360.02</v>
       </c>
       <c r="N2" t="n">
-        <v>49071621.04</v>
+        <v>-424968360.02</v>
       </c>
       <c r="O2" t="n">
-        <v>-230159002.25</v>
-      </c>
-      <c r="P2" t="n">
-        <v>279230623.29</v>
-      </c>
+        <v>-424968360.02</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>569567979.04</v>
+        <v>661422900.47</v>
       </c>
       <c r="R2" t="n">
-        <v>198944031</v>
+        <v>114000000</v>
       </c>
       <c r="S2" t="n">
-        <v>-58972515</v>
+        <v>11880000</v>
       </c>
       <c r="T2" t="n">
-        <v>27485</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-59000000</v>
-      </c>
+        <v>11880000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>519163399.82</v>
+        <v>757337434.33</v>
       </c>
       <c r="W2" t="n">
-        <v>519163399.82</v>
+        <v>757337434.33</v>
       </c>
       <c r="X2" t="n">
-        <v>-89566936.78</v>
+        <v>-221794533.86</v>
       </c>
       <c r="Y2" t="n">
-        <v>34080635.38</v>
+        <v>73923604.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>-123647572.16</v>
+        <v>-295718138.41</v>
       </c>
       <c r="AA2" t="n">
-        <v>-753008336.86</v>
+        <v>163003997.64</v>
       </c>
       <c r="AB2" t="n">
-        <v>-810530023.4299999</v>
+        <v>-228614261.98</v>
       </c>
       <c r="AC2" t="n">
-        <v>40934520.78</v>
+        <v>-71936905.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1295319337.26</v>
+        <v>-240646693.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>432435163.04</v>
+        <v>-151052029.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>11419630.01</v>
+        <v>235021365.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>27756892.73</v>
+        <v>31416348.53</v>
       </c>
       <c r="AH2" t="n">
-        <v>361162761.71</v>
+        <v>567297913.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>151439384.3</v>
+        <v>185068430.85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>209723377.41</v>
+        <v>382229482.79</v>
       </c>
       <c r="AK2" t="n">
-        <v>-230908572.86</v>
+        <v>-383691896.26</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5889724.08</v>
+        <v>-1167623.59</v>
       </c>
       <c r="AM2" t="n">
-        <v>-276470868.87</v>
+        <v>134942156.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>-753008336.86</v>
+        <v>163003997.64</v>
       </c>
       <c r="AO2" t="n">
-        <v>34315206.21</v>
+        <v>-28682557.47</v>
       </c>
       <c r="AP2" t="n">
-        <v>51193759.41</v>
+        <v>32629361.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-23236557.5</v>
+        <v>-7313449.61</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1938111950.05</v>
+        <v>-2177622428.49</v>
       </c>
       <c r="AS2" t="n">
-        <v>-160964571.21</v>
+        <v>111719277.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>-248953456.2</v>
+        <v>-296733901.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1528193922.64</v>
+        <v>-1992607804.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>1122831205.07</v>
+        <v>2343993072.04</v>
       </c>
       <c r="AW2" t="n">
-        <v>-612481297.65</v>
+        <v>297108367.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1735312502.72</v>
+        <v>2046884704.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>528732692.77</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-101901636.78</v>
-      </c>
+        <v>-40689714.4</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>197716367.72</v>
+        <v>100000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-241565633.61</v>
+        <v>-293820490.06</v>
       </c>
       <c r="F3" t="n">
-        <v>2219565641.13</v>
+        <v>1594485288.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1594485288.56</v>
+        <v>1405460719.97</v>
       </c>
       <c r="H3" t="n">
-        <v>-167400.76</v>
+        <v>1938502.67</v>
       </c>
       <c r="I3" t="n">
-        <v>625247753.33</v>
+        <v>187086065.92</v>
       </c>
       <c r="J3" t="n">
-        <v>72855048.23999999</v>
+        <v>269802564.17</v>
       </c>
       <c r="K3" t="n">
-        <v>-16858248.35</v>
+        <v>174399792.36</v>
       </c>
       <c r="L3" t="n">
-        <v>-6101434.35</v>
+        <v>-4597228.19</v>
       </c>
       <c r="M3" t="n">
-        <v>95814730.94</v>
+        <v>100000000</v>
       </c>
       <c r="N3" t="n">
-        <v>95814730.94</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-101901636.78</v>
-      </c>
+        <v>100000000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>197716367.72</v>
+        <v>100000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-217905621.29</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>-335847273.91</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-57000000</v>
+      </c>
       <c r="S3" t="n">
-        <v>-26840229.01</v>
+        <v>28436.14</v>
       </c>
       <c r="T3" t="n">
-        <v>64159770.99</v>
+        <v>10028436.14</v>
       </c>
       <c r="U3" t="n">
-        <v>-91000000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>19740683.07</v>
-      </c>
-      <c r="W3" t="n">
-        <v>19740683.07</v>
-      </c>
+        <v>-10000000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-210806075.35</v>
+        <v>-278875710.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>30759558.26</v>
+        <v>14944780.01</v>
       </c>
       <c r="Z3" t="n">
-        <v>-241565633.61</v>
+        <v>-293820490.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>770298326.38</v>
+        <v>253130775.66</v>
       </c>
       <c r="AB3" t="n">
-        <v>473353776.38</v>
+        <v>509831442.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4910853.43</v>
+        <v>395736666.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1145643024.7</v>
+        <v>-91864571.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>-210575921.06</v>
+        <v>2898692.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>-456802473.83</v>
+        <v>203060654.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8786164.619999999</v>
+        <v>14651810.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>429263115.84</v>
+        <v>510506587.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>184015299.99</v>
+        <v>183710713.56</v>
       </c>
       <c r="AJ3" t="n">
-        <v>245247815.85</v>
+        <v>326795873.84</v>
       </c>
       <c r="AK3" t="n">
-        <v>-625234</v>
+        <v>20251363.86</v>
       </c>
       <c r="AL3" t="n">
-        <v>-1570004.55</v>
+        <v>631858.64</v>
       </c>
       <c r="AM3" t="n">
-        <v>-199210676.33</v>
+        <v>-1574950273.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>770298326.38</v>
+        <v>253130775.66</v>
       </c>
       <c r="AO3" t="n">
-        <v>239441737.96</v>
+        <v>147693038.89</v>
       </c>
       <c r="AP3" t="n">
-        <v>33887734.92</v>
+        <v>30923849.76</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-11060640.8</v>
+        <v>-9914006.109999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2605776244.73</v>
+        <v>-2493779890.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>-157724758.57</v>
+        <v>-75873646.19</v>
       </c>
       <c r="AT3" t="n">
-        <v>-252049009.4</v>
+        <v>-240587488.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>-2196002476.76</v>
+        <v>-2177318755.85</v>
       </c>
       <c r="AV3" t="n">
-        <v>3113805739.03</v>
+        <v>2578207783.94</v>
       </c>
       <c r="AW3" t="n">
-        <v>956005655.48</v>
+        <v>316018059.74</v>
       </c>
       <c r="AX3" t="n">
-        <v>2157800083.55</v>
+        <v>2262189724.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-40689714.4</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>528732692.77</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-101901636.78</v>
+      </c>
       <c r="D4" t="n">
-        <v>100000000</v>
+        <v>197716367.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-293820490.06</v>
+        <v>-241565633.61</v>
       </c>
       <c r="F4" t="n">
+        <v>2219565641.13</v>
+      </c>
+      <c r="G4" t="n">
         <v>1594485288.56</v>
       </c>
-      <c r="G4" t="n">
-        <v>1405460719.97</v>
-      </c>
       <c r="H4" t="n">
-        <v>1938502.67</v>
+        <v>-167400.76</v>
       </c>
       <c r="I4" t="n">
-        <v>187086065.92</v>
+        <v>625247753.33</v>
       </c>
       <c r="J4" t="n">
-        <v>269802564.17</v>
+        <v>72855048.23999999</v>
       </c>
       <c r="K4" t="n">
-        <v>174399792.36</v>
+        <v>-16858248.35</v>
       </c>
       <c r="L4" t="n">
-        <v>-4597228.19</v>
+        <v>-6101434.35</v>
       </c>
       <c r="M4" t="n">
-        <v>100000000</v>
+        <v>95814730.94</v>
       </c>
       <c r="N4" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>95814730.94</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-101901636.78</v>
+      </c>
       <c r="P4" t="n">
-        <v>100000000</v>
+        <v>197716367.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>-335847273.91</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-57000000</v>
-      </c>
+        <v>-217905621.29</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>28436.14</v>
+        <v>-26840229.01</v>
       </c>
       <c r="T4" t="n">
-        <v>10028436.14</v>
+        <v>64159770.99</v>
       </c>
       <c r="U4" t="n">
-        <v>-10000000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-91000000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19740683.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19740683.07</v>
+      </c>
       <c r="X4" t="n">
-        <v>-278875710.05</v>
+        <v>-210806075.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>14944780.01</v>
+        <v>30759558.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>-293820490.06</v>
+        <v>-241565633.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>253130775.66</v>
+        <v>770298326.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>509831442.67</v>
+        <v>473353776.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>395736666.72</v>
+        <v>-4910853.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>-91864571.11</v>
+        <v>1145643024.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>2898692.13</v>
+        <v>-210575921.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>203060654.93</v>
+        <v>-456802473.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>14651810.68</v>
+        <v>-8786164.619999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>510506587.4</v>
+        <v>429263115.84</v>
       </c>
       <c r="AI4" t="n">
-        <v>183710713.56</v>
+        <v>184015299.99</v>
       </c>
       <c r="AJ4" t="n">
-        <v>326795873.84</v>
+        <v>245247815.85</v>
       </c>
       <c r="AK4" t="n">
-        <v>20251363.86</v>
+        <v>-625234</v>
       </c>
       <c r="AL4" t="n">
-        <v>631858.64</v>
+        <v>-1570004.55</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1574950273.9</v>
+        <v>-199210676.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>253130775.66</v>
+        <v>770298326.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>147693038.89</v>
+        <v>239441737.96</v>
       </c>
       <c r="AP4" t="n">
-        <v>30923849.76</v>
+        <v>33887734.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-9914006.109999999</v>
+        <v>-11060640.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2493779890.82</v>
+        <v>-2605776244.73</v>
       </c>
       <c r="AS4" t="n">
-        <v>-75873646.19</v>
+        <v>-157724758.57</v>
       </c>
       <c r="AT4" t="n">
-        <v>-240587488.78</v>
+        <v>-252049009.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2177318755.85</v>
+        <v>-2196002476.76</v>
       </c>
       <c r="AV4" t="n">
-        <v>2578207783.94</v>
+        <v>3113805739.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>316018059.74</v>
+        <v>956005655.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>2262189724.2</v>
+        <v>2157800083.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-132714140.77</v>
+        <v>-876655909.02</v>
       </c>
       <c r="C5" t="n">
-        <v>-424968360.02</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>-230159002.25</v>
+      </c>
+      <c r="D5" t="n">
+        <v>279230623.29</v>
+      </c>
       <c r="E5" t="n">
-        <v>-295718138.41</v>
+        <v>-123647572.16</v>
       </c>
       <c r="F5" t="n">
-        <v>1405460719.97</v>
+        <v>1892427025.43</v>
       </c>
       <c r="G5" t="n">
-        <v>1108979227.18</v>
+        <v>2219565641.13</v>
       </c>
       <c r="H5" t="n">
-        <v>-1606605.3</v>
+        <v>3507312.69</v>
       </c>
       <c r="I5" t="n">
-        <v>298088098.09</v>
+        <v>-330645928.39</v>
       </c>
       <c r="J5" t="n">
-        <v>-526338800.02</v>
+        <v>-147205570.57</v>
       </c>
       <c r="K5" t="n">
-        <v>-86998085</v>
+        <v>-187085869.53</v>
       </c>
       <c r="L5" t="n">
-        <v>-14372355</v>
+        <v>-9191322.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-424968360.02</v>
+        <v>49071621.04</v>
       </c>
       <c r="N5" t="n">
-        <v>-424968360.02</v>
+        <v>49071621.04</v>
       </c>
       <c r="O5" t="n">
-        <v>-424968360.02</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>-230159002.25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>279230623.29</v>
+      </c>
       <c r="Q5" t="n">
-        <v>661422900.47</v>
+        <v>569567979.04</v>
       </c>
       <c r="R5" t="n">
-        <v>114000000</v>
+        <v>198944031</v>
       </c>
       <c r="S5" t="n">
-        <v>11880000</v>
+        <v>-58972515</v>
       </c>
       <c r="T5" t="n">
-        <v>11880000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>27485</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-59000000</v>
+      </c>
       <c r="V5" t="n">
-        <v>757337434.33</v>
+        <v>519163399.82</v>
       </c>
       <c r="W5" t="n">
-        <v>757337434.33</v>
+        <v>519163399.82</v>
       </c>
       <c r="X5" t="n">
-        <v>-221794533.86</v>
+        <v>-89566936.78</v>
       </c>
       <c r="Y5" t="n">
-        <v>73923604.55</v>
+        <v>34080635.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>-295718138.41</v>
+        <v>-123647572.16</v>
       </c>
       <c r="AA5" t="n">
-        <v>163003997.64</v>
+        <v>-753008336.86</v>
       </c>
       <c r="AB5" t="n">
-        <v>-228614261.98</v>
+        <v>-810530023.4299999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-71936905.05</v>
+        <v>40934520.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>-240646693.06</v>
+        <v>-1295319337.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>-151052029.85</v>
+        <v>432435163.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>235021365.98</v>
+        <v>11419630.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>31416348.53</v>
+        <v>27756892.73</v>
       </c>
       <c r="AH5" t="n">
-        <v>567297913.64</v>
+        <v>361162761.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>185068430.85</v>
+        <v>151439384.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>382229482.79</v>
+        <v>209723377.41</v>
       </c>
       <c r="AK5" t="n">
-        <v>-383691896.26</v>
+        <v>-230908572.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1167623.59</v>
+        <v>-5889724.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>134942156.59</v>
+        <v>-276470868.87</v>
       </c>
       <c r="AN5" t="n">
-        <v>163003997.64</v>
+        <v>-753008336.86</v>
       </c>
       <c r="AO5" t="n">
-        <v>-28682557.47</v>
+        <v>34315206.21</v>
       </c>
       <c r="AP5" t="n">
-        <v>32629361.17</v>
+        <v>51193759.41</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-7313449.61</v>
+        <v>-23236557.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2177622428.49</v>
+        <v>-1938111950.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>111719277.2</v>
+        <v>-160964571.21</v>
       </c>
       <c r="AT5" t="n">
-        <v>-296733901.58</v>
+        <v>-248953456.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1992607804.11</v>
+        <v>-1528193922.64</v>
       </c>
       <c r="AV5" t="n">
-        <v>2343993072.04</v>
+        <v>1122831205.07</v>
       </c>
       <c r="AW5" t="n">
-        <v>297108367.7</v>
+        <v>-612481297.65</v>
       </c>
       <c r="AX5" t="n">
-        <v>2046884704.34</v>
+        <v>1735312502.72</v>
       </c>
     </row>
   </sheetData>
@@ -3890,197 +3890,197 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
       <c r="DO1" t="inlineStr">
         <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Ming  Qin', 'age': 47, 'title': 'CEO &amp; Director', 'yearBorn': 1978, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Lixiang  Luo', 'age': 53, 'title': 'CFO &amp; Financial Director', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ying  Yin', 'age': 53, 'title': 'Chief Human Resources Officer', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Bo  Lin', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jiang  Zhichun', 'title': 'General Manager of HAIMA Automobile Sales', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ming Shi Lin', 'title': 'Vice President', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Li  Zheng', 'age': 38, 'title': 'Secretary to the Board', 'yearBorn': 1987, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -4185,28 +4185,28 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>4.6</v>
+        <v>4.06</v>
       </c>
       <c r="V2" t="n">
-        <v>4.87</v>
+        <v>4.09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.47</v>
+        <v>3.86</v>
       </c>
       <c r="X2" t="n">
-        <v>4.65</v>
+        <v>4.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.87</v>
+        <v>4.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.47</v>
+        <v>3.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.65</v>
+        <v>4.06</v>
       </c>
       <c r="AC2" t="n">
         <v>1466985600</v>
@@ -4215,31 +4215,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.591</v>
+        <v>0.416</v>
       </c>
       <c r="AF2" t="n">
-        <v>32.142857</v>
+        <v>28.571428</v>
       </c>
       <c r="AG2" t="n">
-        <v>32921146</v>
+        <v>49776900</v>
       </c>
       <c r="AH2" t="n">
-        <v>32921146</v>
+        <v>49776900</v>
       </c>
       <c r="AI2" t="n">
-        <v>60771531</v>
+        <v>54433615</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38530089</v>
+        <v>40549371</v>
       </c>
       <c r="AK2" t="n">
-        <v>38530089</v>
+        <v>40549371</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.51</v>
+        <v>4.01</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4248,10 +4248,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>7400863744</v>
+        <v>6578545664</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7400863917</v>
+        <v>6677223889</v>
       </c>
       <c r="AR2" t="n">
         <v>3.7</v>
@@ -4266,13 +4266,13 @@
         <v>1.198224</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.0993137</v>
+        <v>3.6438344</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5422</v>
+        <v>5.0774</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.75165</v>
+        <v>6.7173</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4289,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>7708223488</v>
+        <v>6885905408</v>
       </c>
       <c r="BD2" t="n">
         <v>-0.0832</v>
@@ -4313,7 +4313,7 @@
         <v>0.958</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.697286</v>
+        <v>4.1753654</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4342,16 +4342,16 @@
         <v>1188777600</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.27</v>
+        <v>3.814</v>
       </c>
       <c r="BU2" t="n">
-        <v>181.231</v>
+        <v>161.897</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.111111164</v>
+        <v>0.043701768</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BX2" t="n">
         <v>0.05</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4466,148 +4466,148 @@
       </c>
       <c r="DC2" t="inlineStr">
         <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-1.4778311</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>1780038249</v>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="n">
+        <v>1782111897</v>
+      </c>
+      <c r="DH2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>finmb_11381883</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DL2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DN2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>-2.173911</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>HAIMA AUTOMOBILE CO LTD</t>
+          <t>Haima Automobile Co.,Ltd.</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>Haima Automobile Co.,Ltd</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>HAIMA AUTOMOBILE CO LTD</t>
+        </is>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
         <v>776309400000</v>
       </c>
-      <c r="DS2" t="n">
-        <v>-0.099999905</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>4.47 - 4.65</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DU2" t="n">
+        <v>-0.059999943</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>3.86 - 4.06</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DV2" t="n">
-        <v>60771531</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.79999995</v>
-      </c>
       <c r="DX2" t="n">
-        <v>0.2162162</v>
-      </c>
-      <c r="DY2" t="inlineStr">
+        <v>54433615</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.29999995</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.08108107000000001</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>3.7 - 12.03</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
-        <v>-7.5299997</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.6259351399999999</v>
-      </c>
       <c r="EB2" t="n">
-        <v>11.111116</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="EC2" t="n">
+        <v>-0.66749793</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>4.370177</v>
+      </c>
+      <c r="EE2" t="n">
         <v>1619693940</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EF2" t="n">
         <v>1619693940</v>
       </c>
-      <c r="EE2" t="n">
+      <c r="EG2" t="n">
         <v>-0.09</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EH2" t="n">
         <v>0.14</v>
       </c>
-      <c r="EG2" t="n">
-        <v>-1.0422001</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.18804808</v>
-      </c>
       <c r="EI2" t="n">
-        <v>-2.2516499</v>
+        <v>-1.0774002</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.33349624</v>
+        <v>-0.21219525</v>
       </c>
       <c r="EK2" t="n">
+        <v>-2.7173</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.40452266</v>
+      </c>
+      <c r="EM2" t="n">
         <v>15</v>
       </c>
-      <c r="EL2" t="n">
+      <c r="EN2" t="n">
         <v>15</v>
       </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Haima Automobile Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Haima Automobile Co.,Ltd</t>
+        </is>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
